--- a/PTBR/Lang/PTBR/Dialog/Drama/guild_clerk.xlsx
+++ b/PTBR/Lang/PTBR/Dialog/Drama/guild_clerk.xlsx
@@ -446,7 +446,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oh, parece que você não é um membro da #guild. Como conseguiu entrar?  </t>
+          <t>Oh, parece que você não é membro da #guild. Como entrou aqui?</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oh, parece que você não é um membro da #guild. Como conseguiu entrar?  </t>
+          <t>Oh, parece que você não é membro da #guild. Como entrou aqui?</t>
         </is>
       </c>
     </row>
@@ -516,7 +516,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oh, parece que você não é um membro da #guild. Como conseguiu entrar?  </t>
+          <t>Oh, parece que você não é membro da #guild. Como entrou aqui?</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fale com Lady Marian se quiser se juntar à #guild.  </t>
+          <t>Fale com a Lady Marian, se quiser entrar na #guild.</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bem-vindo de volta à #guild, #pc. Seu cargo atual é "#guild_title". O que posso fazer por você hoje?  </t>
+          <t>Bem-vindo de volta à #guild, #pc. Seu posto atual é "#guild_title". O que posso fazer por você hoje?</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Me fale sobre a guilda.  </t>
+          <t>Fale-me da guilda.</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quero ser promovido.  </t>
+          <t>Quero subir de posto.</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Night Shroud é um santuário para os marginais que vivem no submundo. Aqui, nenhum pecador é acusado por seu passado. Nosso mestre da guilda é conhecido como "The Night Bringer", e dizem que ninguém jamais viu seu verdadeiro rosto.  </t>
+          <t>A "Manto da Noite" é um santuário para os cafajestos do submundo. Aqui, nenhum pecador jamais é acusado pelo passado. Nosso mestre da guilda é conhecido como "O Portador da Noite", e corre rumor de que ninguém jamais viu sua verdadeira face.</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Guilda dos Magos possui um excelente sistema educacional que outras guildas não têm. Estudantes de toda Tyris vêm em busca de conhecimento. O mestre da escola, Jorg, admite ser um esnobe, mas é um gênio quando se trata de dinheiro e política.  </t>
+          <t>A Guilda dos Magos tem um sistema educacional excelente que as outras guildas não têm. Estudantes vêm de toda Tyris buscando conhecimento. O mestre da escola, Jorg, é um esnobe reconhecido, por conta própria, mas um gênio quando o assunto é dinheiro e política.</t>
         </is>
       </c>
     </row>
@@ -747,7 +747,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Guilda dos Lutadores está cheia de aventureiros orgulhosos de sua força. Thorran é um homem rígido, mas não hesita em declarar guerra contra uma nação para proteger os membros de sua guilda. Graças a ele, estamos todos unidos por um forte laço, como uma família.  </t>
+          <t>A Guilda dos Lutadores está cheia de aventureiros orgulhosos da própria força. Thorran é um homem duro, mas não hesitaria em declarar guerra a uma nação para proteger os membros da guilda. Graças a ele, todos nós somos atados por um laço forte, como família.</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Guilda dos Mercadores apoia os comerciantes, garantindo que possam negociar com segurança e justiça. Lady Marian pode parecer um pouco intimidadora, mas é uma empresária formidável que acumulou uma fortuna em Tyris em apenas uma geração.  </t>
+          <t>A Guilda dos Mercadores apoia os mercadores, garantindo que negociem com segurança e justiça. A Lady Marian pode ser um pouco intimidadora, mas é uma empresária formidável que amassou uma fortuna em Tyris em apenas uma geração.</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Se falar comigo quando sua contribuição for suficiente, poderá aumentar seu posto na #guild. Você poderá acessar serviços de nível mais alto conforme avança no ranking, então faça o seu melhor para subir.  </t>
+          <t>Se falar comigo quando sua contribuição for suficiente, você sobe de posto na #guild. Conforme avança, pode usar serviços de nível mais alto, então faça o seu melhor para subir.</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parece que você atende aos requisitos para o próximo nível. Parabéns, você foi promovido!  </t>
+          <t>Você parece cumprir os requisitos do próximo nível. Parabéns, você foi promovido!</t>
         </is>
       </c>
     </row>
@@ -884,7 +884,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Infelizmente, não podemos aprovar sua promoção neste momento.  </t>
+          <t>Infelizmente, não podemos aprovar sua promoção neste momento.</t>
         </is>
       </c>
     </row>
